--- a/employee_input.xlsx
+++ b/employee_input.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pwcindia-my.sharepoint.com/personal/deborshi_som_pwc_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pwcindia-my.sharepoint.com/personal/abhinandan_roy_pwc_com/Documents/Documents/work-in-sync/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{2480ABF1-70E0-4400-B164-214693FD6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE20E2D-E6AA-487E-BA77-A6F30A928B7D}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="8_{2480ABF1-70E0-4400-B164-214693FD6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C202E1B8-48BA-4D89-BC56-15BF11539271}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{887FC20F-A5A9-424F-A0B9-DA167AEAA032}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Employee_Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>employee_id</t>
   </si>
@@ -47,22 +47,28 @@
     <t>employee_name</t>
   </si>
   <si>
+    <t>Anik Tanzim</t>
+  </si>
+  <si>
+    <t>Deborshi Som</t>
+  </si>
+  <si>
+    <t>Abhinandan Roy</t>
+  </si>
+  <si>
     <t>Oindrila Chakraborty</t>
   </si>
   <si>
     <t>Subhabrata Sengupta</t>
   </si>
   <si>
-    <t xml:space="preserve">Ishita Banerjee </t>
+    <t>Ishita Banerjee</t>
   </si>
   <si>
     <t>REDDI KEERTHI</t>
   </si>
   <si>
-    <t>Anik Tanzim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anusree Roy </t>
+    <t>Anusree Roy</t>
   </si>
   <si>
     <t>Kumari Ritul</t>
@@ -71,37 +77,37 @@
     <t>Moupriya Ganguly</t>
   </si>
   <si>
-    <t xml:space="preserve">Ayantik Das </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratul Ghosh </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avisake Chowdhury </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banavathu Naik </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Piyush Deb </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shreya Singh </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riya Biswas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soumya Mondal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sayanti Pal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arunabha Mitra </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solanki Kundu </t>
+    <t>Ayantik Das</t>
+  </si>
+  <si>
+    <t>Ratul Ghosh</t>
+  </si>
+  <si>
+    <t>Avisake Chowdhury</t>
+  </si>
+  <si>
+    <t>Banavathu Naik</t>
+  </si>
+  <si>
+    <t>Piyush Deb</t>
+  </si>
+  <si>
+    <t>Shreya Singh</t>
+  </si>
+  <si>
+    <t>Riya Biswas</t>
+  </si>
+  <si>
+    <t>Soumya Mondal</t>
+  </si>
+  <si>
+    <t>Sayanti Pal</t>
+  </si>
+  <si>
+    <t>Arunabha Mitra</t>
+  </si>
+  <si>
+    <t>Solanki Kundu</t>
   </si>
   <si>
     <t>Sunirmal Bera</t>
@@ -119,9 +125,6 @@
     <t>Kaustav Chakraborty</t>
   </si>
   <si>
-    <t>Deborshi Som</t>
-  </si>
-  <si>
     <t>SAQLAIN Mustafa</t>
   </si>
   <si>
@@ -149,20 +152,32 @@
     <t>Mukul Kumar</t>
   </si>
   <si>
-    <t>Abhinandan Roy</t>
-  </si>
-  <si>
     <t>ISHWAR Jha</t>
   </si>
   <si>
     <t>Vivek Nayak</t>
+  </si>
+  <si>
+    <t>Aditi Khaitan</t>
+  </si>
+  <si>
+    <t>Sumit Shaw</t>
+  </si>
+  <si>
+    <t>Debojyoti Saha</t>
+  </si>
+  <si>
+    <t>Gourab Das</t>
+  </si>
+  <si>
+    <t>Tushti Thakur</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,43 +191,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Display"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -222,12 +202,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -266,16 +240,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -283,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,26 +265,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -327,6 +283,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -646,14 +606,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2370C544-BB0A-49DD-B484-76772E57400F}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" customWidth="1"/>
+    <col min="2" max="2" width="35.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,300 +621,340 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>101588348</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>101582442</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>101578754</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>101560676</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>101560510</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>101560450</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>101560255</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>101453747</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>101442923</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>101442680</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>101442606</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>101442577</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>101442457</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>101442398</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>101408941</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>101282639</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>101259073</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>101148869</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>101110378</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
         <v>101744590</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="4">
+      <c r="B21" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
         <v>101758893</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="4">
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
         <v>101675169</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="4">
+      <c r="B23" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
         <v>101743106</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="4">
+      <c r="B24" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
         <v>101777658</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="4">
+      <c r="B25" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
         <v>101774195</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="4">
+      <c r="B26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
         <v>101779334</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="4">
+      <c r="B27" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
         <v>100682010</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="4">
+      <c r="B28" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
         <v>101752092</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="4">
+      <c r="B29" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
         <v>101675381</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="8">
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
         <v>101786698</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="9">
+      <c r="B31" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
         <v>101699107</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4">
+      <c r="B32" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
         <v>101264925</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="4">
+      <c r="B33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
         <v>101675401</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="4">
+      <c r="B34" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
         <v>101755619</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="4">
+      <c r="B35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
         <v>101675341</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="4">
+      <c r="B36" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
         <v>101787312</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="4">
-        <v>101787312</v>
-      </c>
-      <c r="B38" s="6" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
+        <v>101775278</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
+        <v>101082599</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
+        <v>101807073</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>101790824</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
+        <v>101805990</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>101676413</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/employee_input.xlsx
+++ b/employee_input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pwcindia-my.sharepoint.com/personal/abhinandan_roy_pwc_com/Documents/Documents/work-in-sync/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pwcindia-my.sharepoint.com/personal/abhinandan_roy_pwc_com/Documents/work-in-sync/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{2480ABF1-70E0-4400-B164-214693FD6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C202E1B8-48BA-4D89-BC56-15BF11539271}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{2480ABF1-70E0-4400-B164-214693FD6CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87332863-1F17-4233-AB5A-6E99774796D0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{887FC20F-A5A9-424F-A0B9-DA167AEAA032}"/>
   </bookViews>
@@ -170,7 +170,7 @@
     <t>Gourab Das</t>
   </si>
   <si>
-    <t>Tushti Thakur</t>
+    <t>Pankaj Devidas Bhagwat</t>
   </si>
 </sst>
 </file>
@@ -283,10 +283,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -951,7 +947,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
-        <v>101676413</v>
+        <v>101756438</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>43</v>
